--- a/data/trans_dic/P29A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P29A_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas</t>
+          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,49; 63,88</t>
+          <t>54,57; 63,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,89; 69,18</t>
+          <t>58,76; 68,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,34; 70,86</t>
+          <t>60,95; 70,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,51; 60,6</t>
+          <t>51,25; 60,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,87; 44,65</t>
+          <t>34,02; 45,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,52; 48,15</t>
+          <t>36,21; 48,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,47; 48,36</t>
+          <t>37,33; 48,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,24; 39,99</t>
+          <t>32,39; 40,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47,55; 55,07</t>
+          <t>47,6; 55,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50,65; 58,66</t>
+          <t>51,13; 58,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,32; 59,86</t>
+          <t>51,79; 59,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,87; 50,01</t>
+          <t>43,68; 50,18</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>53,58; 64,28</t>
+          <t>53,72; 64,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,09; 62,98</t>
+          <t>52,92; 63,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,78; 67,75</t>
+          <t>57,09; 67,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42,13; 51,69</t>
+          <t>42,5; 51,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,09; 43,34</t>
+          <t>33,13; 42,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,76; 43,27</t>
+          <t>31,82; 42,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,39; 54,63</t>
+          <t>43,33; 54,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,06; 39,36</t>
+          <t>31,22; 39,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,79; 52,26</t>
+          <t>44,52; 52,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,15; 52,79</t>
+          <t>44,75; 52,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,96; 59,51</t>
+          <t>51,74; 59,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,62; 45,26</t>
+          <t>38,23; 44,82</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,09; 64,46</t>
+          <t>55,84; 63,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,38; 61,71</t>
+          <t>53,24; 61,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,63; 66,36</t>
+          <t>57,81; 66,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,43; 51,06</t>
+          <t>12,24; 51,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,11; 41,64</t>
+          <t>26,61; 40,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,18; 31,16</t>
+          <t>20,12; 31,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,37; 39,34</t>
+          <t>24,54; 40,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,44; 29,81</t>
+          <t>19,25; 30,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,8; 57,85</t>
+          <t>49,94; 57,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,17; 51,34</t>
+          <t>44,6; 51,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50,91; 58,74</t>
+          <t>51,02; 58,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,76; 43,93</t>
+          <t>15,49; 43,91</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,38; 54,05</t>
+          <t>48,48; 54,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,83; 55,93</t>
+          <t>49,95; 56,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,23; 58,25</t>
+          <t>51,97; 58,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,9; 53,1</t>
+          <t>46,11; 52,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,62; 29,42</t>
+          <t>22,8; 29,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,96; 29,49</t>
+          <t>22,68; 29,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,82; 37,29</t>
+          <t>31,17; 37,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,36; 67,47</t>
+          <t>26,28; 71,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,7; 44,22</t>
+          <t>39,51; 44,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,59; 44,37</t>
+          <t>39,76; 44,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43,94; 48,94</t>
+          <t>43,76; 48,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,15; 61,44</t>
+          <t>39,31; 61,96</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>53,19; 63,86</t>
+          <t>52,86; 64,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,62; 61,31</t>
+          <t>51,99; 61,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44,54; 52,9</t>
+          <t>44,91; 53,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,16; 53,74</t>
+          <t>44,19; 54,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,38; 26,14</t>
+          <t>19,0; 26,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,9; 24,2</t>
+          <t>17,87; 23,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,24; 26,87</t>
+          <t>20,5; 27,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,66; 18,69</t>
+          <t>11,36; 18,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,01; 39,65</t>
+          <t>33,37; 39,54</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32,34; 37,85</t>
+          <t>31,88; 37,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32,58; 38,1</t>
+          <t>32,58; 37,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,3; 30,75</t>
+          <t>22,41; 30,83</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,55; 51,18</t>
+          <t>39,28; 50,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,28; 56,24</t>
+          <t>43,86; 55,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,69; 59,32</t>
+          <t>47,24; 59,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29,3; 51,78</t>
+          <t>28,94; 51,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,84; 17,91</t>
+          <t>13,82; 17,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,48; 23,68</t>
+          <t>18,27; 23,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,14; 25,26</t>
+          <t>19,89; 25,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,37; 19,17</t>
+          <t>13,49; 19,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,3; 23,38</t>
+          <t>19,44; 23,53</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,15; 28,97</t>
+          <t>23,98; 28,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,59; 31,46</t>
+          <t>26,27; 31,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,48; 25,9</t>
+          <t>18,56; 25,51</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,42; 56,75</t>
+          <t>53,24; 56,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>54,4; 57,95</t>
+          <t>54,43; 57,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55,22; 58,75</t>
+          <t>55,49; 58,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,03; 50,11</t>
+          <t>33,75; 49,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,13; 25,96</t>
+          <t>22,96; 26,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,29; 27,31</t>
+          <t>24,15; 27,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,06; 32,29</t>
+          <t>29,09; 32,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,32; 42,66</t>
+          <t>23,21; 43,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,23; 40,74</t>
+          <t>38,25; 40,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39,29; 41,72</t>
+          <t>39,39; 41,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42,35; 44,89</t>
+          <t>42,33; 44,74</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,1; 42,63</t>
+          <t>33,35; 42,15</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas</t>
+          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>251980; 295437</t>
+          <t>252350; 294161</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>246727; 289833</t>
+          <t>246179; 287896</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>256277; 296065</t>
+          <t>254676; 294701</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>260248; 306152</t>
+          <t>258925; 306776</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>103124; 135940</t>
+          <t>103591; 138212</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>112193; 147927</t>
+          <t>111249; 148806</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>125182; 161560</t>
+          <t>124707; 162036</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>144281; 178939</t>
+          <t>144924; 180045</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>364665; 422317</t>
+          <t>365088; 421997</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>367810; 425957</t>
+          <t>371317; 424597</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>393424; 450113</t>
+          <t>389426; 447975</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>417969; 476458</t>
+          <t>416159; 478093</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>195214; 234197</t>
+          <t>195728; 235061</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>213764; 253550</t>
+          <t>213066; 254573</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>208656; 248980</t>
+          <t>209801; 247595</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>190511; 233748</t>
+          <t>192207; 234416</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>121586; 159286</t>
+          <t>121746; 157293</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>103893; 141566</t>
+          <t>104083; 138939</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>157339; 198070</t>
+          <t>157106; 199140</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>118422; 150074</t>
+          <t>119031; 150193</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>327770; 382418</t>
+          <t>325780; 382111</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>329461; 385214</t>
+          <t>326544; 385686</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>379376; 434446</t>
+          <t>377748; 434701</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>321926; 377193</t>
+          <t>318602; 373562</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>299548; 344219</t>
+          <t>298205; 341337</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316312; 365662</t>
+          <t>315429; 366750</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>289962; 333904</t>
+          <t>290847; 334692</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82989; 341003</t>
+          <t>81719; 345020</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45488; 69868</t>
+          <t>44643; 68492</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50622; 78189</t>
+          <t>50489; 78115</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39504; 63768</t>
+          <t>39773; 65011</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32292; 49523</t>
+          <t>31971; 50974</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349504; 405997</t>
+          <t>350466; 405206</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>372568; 433011</t>
+          <t>376162; 437254</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>338650; 390751</t>
+          <t>339385; 389267</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>106439; 366325</t>
+          <t>129203; 366174</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>591498; 660863</t>
+          <t>592719; 660885</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>550298; 617659</t>
+          <t>551558; 619738</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>580087; 646949</t>
+          <t>577191; 648873</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>472952; 547191</t>
+          <t>475159; 543838</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>160713; 208965</t>
+          <t>161992; 207362</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>171366; 220104</t>
+          <t>169265; 218208</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>252004; 304882</t>
+          <t>254834; 309014</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>257414; 658884</t>
+          <t>256659; 694449</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>767316; 854725</t>
+          <t>763797; 850942</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>732704; 821081</t>
+          <t>735864; 820703</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>847356; 943765</t>
+          <t>843867; 936229</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>785700; 1233061</t>
+          <t>788921; 1243566</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>185434; 222608</t>
+          <t>184260; 224069</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>257114; 299555</t>
+          <t>254020; 299325</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>267445; 317692</t>
+          <t>269690; 319663</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>209005; 254329</t>
+          <t>209111; 255793</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>109556; 147809</t>
+          <t>107414; 148852</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>134797; 182262</t>
+          <t>134606; 180603</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>147334; 195656</t>
+          <t>149236; 196653</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>97644; 156451</t>
+          <t>95105; 152495</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>301711; 362391</t>
+          <t>305053; 361430</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>401545; 470003</t>
+          <t>395868; 466406</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>432884; 506108</t>
+          <t>432833; 501811</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>292210; 403020</t>
+          <t>293663; 404049</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>116361; 150582</t>
+          <t>115555; 148078</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>116337; 147740</t>
+          <t>115212; 146082</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>130885; 166285</t>
+          <t>132415; 167102</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70457; 124546</t>
+          <t>69601; 123566</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>172189; 222752</t>
+          <t>171848; 222039</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>202171; 259122</t>
+          <t>199889; 256247</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>215597; 270493</t>
+          <t>212924; 268832</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>101513; 145585</t>
+          <t>102433; 144453</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>296767; 359515</t>
+          <t>298954; 361851</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>327743; 393063</t>
+          <t>325396; 390395</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>359210; 425029</t>
+          <t>354881; 426801</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>184813; 258981</t>
+          <t>185609; 255062</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1723564; 1830907</t>
+          <t>1717544; 1831220</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1778848; 1894663</t>
+          <t>1779659; 1889648</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1810969; 1926934</t>
+          <t>1819834; 1934005</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1213972; 1688376</t>
+          <t>1137048; 1683124</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>776980; 872060</t>
+          <t>771416; 873674</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>844897; 950267</t>
+          <t>840032; 945286</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1009775; 1122062</t>
+          <t>1010951; 1120415</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>832219; 1522179</t>
+          <t>828328; 1542095</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2517316; 2683147</t>
+          <t>2518645; 2678792</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2651416; 2815308</t>
+          <t>2658260; 2817710</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2860487; 3031962</t>
+          <t>2859140; 3022411</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2296421; 2957516</t>
+          <t>2313769; 2924351</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P29A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P29A_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,21%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,57; 63,61</t>
+          <t>54,28; 64,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,76; 68,71</t>
+          <t>58,6; 68,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,95; 70,53</t>
+          <t>61,46; 70,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51,25; 60,72</t>
+          <t>50,53; 60,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,02; 45,4</t>
+          <t>33,42; 44,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,21; 48,44</t>
+          <t>36,77; 48,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,33; 48,5</t>
+          <t>37,37; 48,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,39; 40,24</t>
+          <t>31,93; 39,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47,6; 55,02</t>
+          <t>47,45; 55,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51,13; 58,47</t>
+          <t>51,15; 58,69</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51,79; 59,58</t>
+          <t>52,1; 59,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,68; 50,18</t>
+          <t>43,31; 49,22</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>53,72; 64,52</t>
+          <t>53,4; 64,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,92; 63,23</t>
+          <t>53,05; 64,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57,09; 67,38</t>
+          <t>56,73; 66,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42,5; 51,84</t>
+          <t>41,55; 51,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,13; 42,8</t>
+          <t>32,98; 43,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,82; 42,47</t>
+          <t>32,06; 43,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,33; 54,92</t>
+          <t>43,96; 54,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,22; 39,39</t>
+          <t>30,92; 38,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,52; 52,21</t>
+          <t>44,96; 52,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,75; 52,85</t>
+          <t>45,17; 52,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,74; 59,54</t>
+          <t>51,87; 59,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,23; 44,82</t>
+          <t>38,08; 43,93</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>41,7%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,84; 63,92</t>
+          <t>55,55; 64,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,24; 61,9</t>
+          <t>52,84; 61,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,81; 66,52</t>
+          <t>57,53; 66,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,24; 51,66</t>
+          <t>43,46; 52,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,61; 40,82</t>
+          <t>26,54; 41,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,12; 31,13</t>
+          <t>20,51; 31,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,54; 40,11</t>
+          <t>24,13; 39,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,25; 30,68</t>
+          <t>19,74; 30,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,94; 57,74</t>
+          <t>50,07; 57,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,6; 51,84</t>
+          <t>44,48; 51,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,02; 58,52</t>
+          <t>51,03; 58,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,49; 43,91</t>
+          <t>37,97; 45,36</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,48; 54,06</t>
+          <t>48,25; 54,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,95; 56,12</t>
+          <t>49,52; 55,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,97; 58,43</t>
+          <t>52,22; 58,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46,11; 52,78</t>
+          <t>44,94; 51,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,8; 29,19</t>
+          <t>22,49; 29,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,68; 29,24</t>
+          <t>22,76; 29,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,17; 37,79</t>
+          <t>31,12; 37,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,28; 71,11</t>
+          <t>24,17; 29,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,51; 44,02</t>
+          <t>39,58; 43,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,76; 44,35</t>
+          <t>39,64; 44,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43,76; 48,55</t>
+          <t>43,85; 48,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,31; 61,96</t>
+          <t>36,73; 41,17</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>52,86; 64,28</t>
+          <t>52,85; 64,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,99; 61,26</t>
+          <t>52,56; 61,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44,91; 53,23</t>
+          <t>44,82; 53,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,19; 54,05</t>
+          <t>40,82; 50,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,0; 26,33</t>
+          <t>19,09; 26,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,87; 23,98</t>
+          <t>17,68; 23,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,5; 27,01</t>
+          <t>20,57; 27,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,36; 18,21</t>
+          <t>16,14; 21,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,37; 39,54</t>
+          <t>32,85; 39,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,88; 37,56</t>
+          <t>32,37; 37,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32,58; 37,77</t>
+          <t>32,4; 37,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,41; 30,83</t>
+          <t>27,01; 32,07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,28; 50,33</t>
+          <t>39,19; 50,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,86; 55,61</t>
+          <t>43,86; 56,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47,24; 59,61</t>
+          <t>47,05; 58,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,94; 51,38</t>
+          <t>27,75; 46,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,82; 17,85</t>
+          <t>13,97; 18,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,27; 23,42</t>
+          <t>18,54; 23,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,89; 25,11</t>
+          <t>19,85; 25,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,02</t>
+          <t>12,83; 17,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,44; 23,53</t>
+          <t>19,49; 23,42</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,98; 28,77</t>
+          <t>23,84; 29,09</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,27; 31,59</t>
+          <t>26,3; 31,5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,56; 25,51</t>
+          <t>17,0; 23,07</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53,24; 56,76</t>
+          <t>53,23; 56,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>54,43; 57,79</t>
+          <t>54,6; 58,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55,49; 58,97</t>
+          <t>55,29; 58,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33,75; 49,95</t>
+          <t>46,01; 49,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,96; 26,01</t>
+          <t>23,03; 25,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,15; 27,17</t>
+          <t>24,32; 27,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,09; 32,24</t>
+          <t>29,28; 32,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,21; 43,22</t>
+          <t>22,86; 25,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,25; 40,68</t>
+          <t>38,21; 40,64</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39,39; 41,75</t>
+          <t>39,2; 41,74</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42,33; 44,74</t>
+          <t>42,38; 44,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,35; 42,15</t>
+          <t>34,46; 36,85</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>283735</t>
+          <t>304682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>162744</t>
+          <t>175414</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>446479</t>
+          <t>480096</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>252350; 294161</t>
+          <t>251005; 296415</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>246179; 287896</t>
+          <t>245523; 288575</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>254676; 294701</t>
+          <t>256796; 295449</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>258925; 306776</t>
+          <t>278202; 330597</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>103591; 138212</t>
+          <t>101744; 136866</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>111249; 148806</t>
+          <t>112948; 150033</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>124707; 162036</t>
+          <t>124841; 162491</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>144924; 180045</t>
+          <t>155958; 192111</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>365088; 421997</t>
+          <t>363887; 423555</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>371317; 424597</t>
+          <t>371443; 426227</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>389426; 447975</t>
+          <t>391757; 447458</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>416159; 478093</t>
+          <t>449990; 511361</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>212965</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>133901</t>
+          <t>145667</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>346866</t>
+          <t>370358</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>195728; 235061</t>
+          <t>194551; 234576</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>213066; 254573</t>
+          <t>213598; 257846</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>209801; 247595</t>
+          <t>208474; 246071</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>192207; 234416</t>
+          <t>200751; 247876</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>121746; 157293</t>
+          <t>121209; 160835</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>104083; 138939</t>
+          <t>104887; 141499</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>157106; 199140</t>
+          <t>159399; 197854</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>119031; 150193</t>
+          <t>130381; 163384</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>325780; 382111</t>
+          <t>329058; 383837</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>326544; 385686</t>
+          <t>329623; 386369</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>377748; 434701</t>
+          <t>378721; 432056</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>318602; 373562</t>
+          <t>344601; 397495</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>210884</t>
+          <t>227684</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>46565</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>251217</t>
+          <t>274249</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>298205; 341337</t>
+          <t>296627; 344710</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315429; 366750</t>
+          <t>313108; 364855</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>290847; 334692</t>
+          <t>289475; 333685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81719; 345020</t>
+          <t>204768; 248332</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44643; 68492</t>
+          <t>44522; 68793</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50489; 78115</t>
+          <t>51471; 78957</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39773; 65011</t>
+          <t>39110; 64633</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31971; 50974</t>
+          <t>36818; 56601</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>350466; 405206</t>
+          <t>351421; 403197</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>376162; 437254</t>
+          <t>375169; 434750</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>339385; 389267</t>
+          <t>339495; 391665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>129203; 366174</t>
+          <t>249734; 298302</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>509939</t>
+          <t>544072</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>414766</t>
+          <t>230439</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>924705</t>
+          <t>774512</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>592719; 660885</t>
+          <t>589878; 661603</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>551558; 619738</t>
+          <t>546901; 616351</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>577191; 648873</t>
+          <t>579929; 647819</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>475159; 543838</t>
+          <t>506643; 578834</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>161992; 207362</t>
+          <t>159732; 207157</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>169265; 218208</t>
+          <t>169877; 219995</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>254834; 309014</t>
+          <t>254477; 309463</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>256659; 694449</t>
+          <t>207734; 255824</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>763797; 850942</t>
+          <t>765013; 849279</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>735864; 820703</t>
+          <t>733606; 819795</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>843867; 936229</t>
+          <t>845535; 936607</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>788921; 1243566</t>
+          <t>729841; 818026</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>231835</t>
+          <t>257777</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>130663</t>
+          <t>152817</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>362498</t>
+          <t>410594</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>184260; 224069</t>
+          <t>184233; 223131</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>254020; 299325</t>
+          <t>256794; 299243</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>269690; 319663</t>
+          <t>269121; 318907</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>209111; 255793</t>
+          <t>231079; 284084</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>107414; 148852</t>
+          <t>107965; 149415</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>134606; 180603</t>
+          <t>133150; 180349</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>149236; 196653</t>
+          <t>149788; 196711</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>95105; 152495</t>
+          <t>133682; 174600</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>305053; 361430</t>
+          <t>300285; 359102</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>395868; 466406</t>
+          <t>401937; 467438</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>432833; 501811</t>
+          <t>430499; 501735</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>293663; 404049</t>
+          <t>376635; 447201</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94860</t>
+          <t>85841</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>122080</t>
+          <t>127207</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>216940</t>
+          <t>213048</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>115555; 148078</t>
+          <t>115303; 148821</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>115212; 146082</t>
+          <t>115209; 147540</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>132415; 167102</t>
+          <t>131877; 165186</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69601; 123566</t>
+          <t>65829; 111258</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>171848; 222039</t>
+          <t>173781; 224680</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>199889; 256247</t>
+          <t>202831; 257735</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>212924; 268832</t>
+          <t>212582; 270136</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>102433; 144453</t>
+          <t>108037; 151009</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>298954; 361851</t>
+          <t>299768; 360175</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>325396; 390395</t>
+          <t>323457; 394788</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>354881; 426801</t>
+          <t>355376; 425516</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>185609; 255062</t>
+          <t>183502; 249044</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1544218</t>
+          <t>1644749</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1004487</t>
+          <t>878109</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2548705</t>
+          <t>2522857</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1717544; 1831220</t>
+          <t>1717242; 1830525</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1779659; 1889648</t>
+          <t>1785304; 1898607</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1819834; 1934005</t>
+          <t>1813523; 1928264</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1137048; 1683124</t>
+          <t>1580921; 1708454</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>771416; 873674</t>
+          <t>773782; 871409</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>840032; 945286</t>
+          <t>846058; 947581</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1010951; 1120415</t>
+          <t>1017638; 1120748</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>828328; 1542095</t>
+          <t>828959; 918711</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2518645; 2678792</t>
+          <t>2516018; 2676494</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2658260; 2817710</t>
+          <t>2645647; 2817141</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2859140; 3022411</t>
+          <t>2862517; 3036891</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2313769; 2924351</t>
+          <t>2433601; 2602207</t>
         </is>
       </c>
     </row>
